--- a/www/terminologies/ValueSet-jdv-mso-resultat-qualitatif-5-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-mso-resultat-qualitatif-5-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260420150250</t>
+    <t>20260706085549</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>retired</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:02:50+01:00</t>
+    <t>2026-07-06T08:55:49+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
